--- a/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,16</t>
+          <t>-1,88; 2,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,54</t>
+          <t>1,04; 5,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,55</t>
+          <t>-1,81; 2,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,76</t>
+          <t>-1,18; 2,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,85; 14,62</t>
+          <t>8,82; 14,89</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 2,73</t>
+          <t>-1,16; 2,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 1,9</t>
+          <t>-0,9; 1,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 9,93</t>
+          <t>6,15; 10,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 2,12</t>
+          <t>-0,75; 2,24</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 62,3</t>
+          <t>-35,98; 59,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,94; 160,88</t>
+          <t>17,29; 158,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,83; 68,67</t>
+          <t>-35,13; 69,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 46,85</t>
+          <t>-15,25; 44,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>113,37; 246,99</t>
+          <t>110,78; 252,9</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 48,47</t>
+          <t>-15,4; 46,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,32; 36,52</t>
+          <t>-14,07; 36,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>92,61; 192,57</t>
+          <t>95,89; 196,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 41,95</t>
+          <t>-11,39; 43,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 1,25</t>
+          <t>-0,65; 1,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,95</t>
+          <t>0,79; 2,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 2,31</t>
+          <t>-0,08; 2,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 1,04</t>
+          <t>-1,76; 0,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,83; 7,12</t>
+          <t>3,79; 7,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 33,02</t>
+          <t>0,09; 31,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,69</t>
+          <t>-0,82; 0,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,59; 4,61</t>
+          <t>2,57; 4,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 20,56</t>
+          <t>0,47; 19,84</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,35; 81,55</t>
+          <t>-27,54; 97,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>25,71; 200,42</t>
+          <t>30,29; 214,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 147,02</t>
+          <t>-3,64; 154,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-37,81; 35,53</t>
+          <t>-39,6; 32,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,27; 243,56</t>
+          <t>86,27; 237,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1042,53</t>
+          <t>1,78; 912,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 28,69</t>
+          <t>-26,03; 32,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,45; 197,43</t>
+          <t>80,25; 193,01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>17,13; 778,16</t>
+          <t>16,6; 697,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 3,71</t>
+          <t>-0,68; 3,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 2,84</t>
+          <t>-1,22; 2,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,39</t>
+          <t>-1,43; 2,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 3,94</t>
+          <t>-0,34; 3,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,3</t>
+          <t>1,02; 5,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,92</t>
+          <t>-0,3; 2,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,06</t>
+          <t>-0,0; 3,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,4</t>
+          <t>0,38; 3,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,84</t>
+          <t>-0,49; 1,97</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,48; 241,75</t>
+          <t>-27,2; 238,01</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-45,89; 186,95</t>
+          <t>-43,01; 165,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 183,14</t>
+          <t>-47,17; 142,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,43; 536,54</t>
+          <t>-23,63; 462,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,87; 645,63</t>
+          <t>26,06; 660,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,66; 433,0</t>
+          <t>-18,59; 340,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 209,03</t>
+          <t>-2,72; 214,05</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>10,45; 233,9</t>
+          <t>13,79; 233,51</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 129,86</t>
+          <t>-17,86; 140,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,03</t>
+          <t>-0,56; 1,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,63</t>
+          <t>0,84; 2,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,44</t>
+          <t>-0,53; 1,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,32</t>
+          <t>-0,69; 1,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,77</t>
+          <t>5,23; 7,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 22,02</t>
+          <t>-0,25; 22,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 0,98</t>
+          <t>-0,31; 1,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,31; 4,89</t>
+          <t>3,4; 5,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 12,74</t>
+          <t>-0,01; 13,38</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,42; 43,72</t>
+          <t>-17,68; 45,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>25,49; 108,87</t>
+          <t>24,1; 106,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,14; 58,13</t>
+          <t>-16,27; 54,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 32,36</t>
+          <t>-13,35; 33,84</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>100,61; 193,25</t>
+          <t>101,73; 190,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 472,48</t>
+          <t>-5,92; 549,04</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,6; 29,42</t>
+          <t>-7,9; 30,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>81,13; 145,25</t>
+          <t>84,78; 148,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 332,05</t>
+          <t>-0,71; 369,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,39</t>
+          <t>0,52</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,75</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>0,76</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 2,15</t>
+          <t>-1,82; 2,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 5,73</t>
+          <t>1,2; 5,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 2,62</t>
+          <t>-1,44; 2,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,65</t>
+          <t>-1,4; 2,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,82; 14,89</t>
+          <t>8,84; 14,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 2,7</t>
+          <t>-1,05; 2,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,89</t>
+          <t>-0,79; 1,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 10,14</t>
+          <t>6,16; 10,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,75; 2,24</t>
+          <t>-0,61; 2,33</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 59,38</t>
+          <t>-35,09; 62,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17,29; 158,44</t>
+          <t>20,78; 162,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 69,44</t>
+          <t>-28,19; 90,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,25; 44,46</t>
+          <t>-18,0; 42,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>110,78; 252,9</t>
+          <t>111,66; 245,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 46,86</t>
+          <t>-14,02; 44,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,07; 36,28</t>
+          <t>-12,36; 38,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>95,89; 196,83</t>
+          <t>95,68; 202,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-11,39; 43,56</t>
+          <t>-9,37; 44,22</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>1,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>9,21</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,15</t>
+          <t>1,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 1,3</t>
+          <t>-0,62; 1,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,96</t>
+          <t>0,91; 2,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 2,4</t>
+          <t>0,36; 2,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 0,95</t>
+          <t>-1,65; 0,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 7,15</t>
+          <t>3,77; 6,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,09; 31,03</t>
+          <t>-0,57; 2,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,78</t>
+          <t>-0,75; 0,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,53</t>
+          <t>2,61; 4,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 19,84</t>
+          <t>0,25; 1,92</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>251,76%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>187,03%</t>
+          <t>39,76%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 97,49</t>
+          <t>-27,04; 81,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30,29; 214,85</t>
+          <t>37,64; 205,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 154,53</t>
+          <t>13,61; 176,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-39,6; 32,36</t>
+          <t>-38,03; 28,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,27; 237,88</t>
+          <t>84,97; 226,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 912,88</t>
+          <t>-12,55; 69,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 32,69</t>
+          <t>-23,49; 36,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>80,25; 193,01</t>
+          <t>81,81; 196,54</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,6; 697,72</t>
+          <t>7,85; 81,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,33</t>
+          <t>0,23</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,61</t>
+          <t>-0,78; 3,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 2,7</t>
+          <t>-1,08; 2,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 2,16</t>
+          <t>-1,54; 2,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 3,78</t>
+          <t>-0,45; 3,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 5,47</t>
+          <t>0,86; 5,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 2,74</t>
+          <t>-0,43; 2,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,08</t>
+          <t>0,1; 3,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,28</t>
+          <t>0,36; 3,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,97</t>
+          <t>-0,57; 1,89</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-27,2; 238,01</t>
+          <t>-27,33; 237,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,01; 165,54</t>
+          <t>-39,48; 174,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-47,17; 142,09</t>
+          <t>-47,93; 130,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 462,28</t>
+          <t>-30,67; 451,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>26,06; 660,5</t>
+          <t>19,23; 744,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 340,88</t>
+          <t>-22,82; 391,67</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 214,05</t>
+          <t>-1,96; 196,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,79; 233,51</t>
+          <t>10,77; 233,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-17,86; 140,31</t>
+          <t>-21,47; 139,19</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,35</t>
+          <t>0,22</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>0,44</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,12</t>
+          <t>-0,51; 1,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,61</t>
+          <t>0,8; 2,8</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 1,32</t>
+          <t>-0,14; 1,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,4</t>
+          <t>-0,67; 1,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,23; 7,78</t>
+          <t>5,18; 7,78</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 22,49</t>
+          <t>-0,82; 1,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 1,01</t>
+          <t>-0,33; 0,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>3,4; 5,01</t>
+          <t>3,35; 4,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 13,38</t>
+          <t>-0,23; 1,08</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>116,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>11,95%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-17,68; 45,81</t>
+          <t>-16,72; 47,46</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>24,1; 106,87</t>
+          <t>24,72; 119,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 54,48</t>
+          <t>-4,53; 68,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 33,84</t>
+          <t>-13,22; 34,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>101,73; 190,14</t>
+          <t>101,41; 190,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 549,04</t>
+          <t>-15,91; 25,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 30,16</t>
+          <t>-8,87; 30,05</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84,78; 148,61</t>
+          <t>82,94; 146,88</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 369,79</t>
+          <t>-5,83; 32,89</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P2A_ner_R-Estudios-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con problemas de nervios, depresión o trastorno mental</t>
+          <t>Población que convive con personas con problemas de nervios, depresión o trastorno mental</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
